--- a/membership_forms/013_join_the_housing_co_operative_mailing_list--membership_forms.xlsx
+++ b/membership_forms/013_join_the_housing_co_operative_mailing_list--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>how_did_you_hear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Interests</t>
+          <t>How did you hear about us?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_did_you_hear</t>
+          <t>how_did_we_contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How did you hear about us?</t>
+          <t>How can we contact you?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,46 +653,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>how_did_you_hear_other</t>
+          <t>mailing_list</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Mailing List</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_frequency</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email Frequency</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_format</t>
+          <t>email_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email Format</t>
+          <t>Email Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>email_format</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Email Format</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mailing_list</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mailing List</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,322 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>How can we send you emails?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>how_can_we_contact</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How can we contact you?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>mailchimp_list</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mailchimp List</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>mailchimp_list_id</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mailchimp List ID</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>mailchimp_list_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mailchimp List Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mailchimp_list_id</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mailchimp List ID</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mailchimp_list_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Mailchimp List Name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>mailchimp_list_id</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Mailchimp List ID</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>mailchimp_list_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Mailchimp List Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>mailchimp_list_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Mailchimp List ID</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mailchimp_list_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mailchimp List Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>mailchimp_list</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Mailchimp List</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>mailchimp_list_id</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Mailchimp List ID</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>mailchimp_list_name</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Mailchimp List Name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1126,58 +827,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>interest_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interest_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interest_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Online Search</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interest_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,58 +895,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_we_contact_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_we_contact_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Word of Mouth</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_we_contact_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Online Search</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_we_contact_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,51 +963,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>email_frequency_choices</t>
+          <t>mailing_list_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>email_frequency_choices</t>
+          <t>mailing_list_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>email_frequency_choices</t>
+          <t>mailing_list_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1335,80 +1036,80 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>email_format_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>email_format_choices</t>
+          <t>email_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plain_text</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plain text</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>email_format_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>email_format_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>plain_text</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Plain text</t>
         </is>
       </c>
     </row>
@@ -1420,231 +1121,95 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mailing_list_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mailing_list_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mailing_list_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>how_can_we_contact_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>how_can_we_contact_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>how_can_we_contact_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>mail</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Mail</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>how_can_we_contact_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>mailchimp_list_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
